--- a/docs/requirements/PRD_IEEE_29148_Checklist.xlsx
+++ b/docs/requirements/PRD_IEEE_29148_Checklist.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5CE276-4ECD-44A7-A566-B785DA625804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="6975" yWindow="1725" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="IEEE 29148 PRD Checklist" state="visible" r:id="rId4"/>
+    <sheet name="IEEE 29148 PRD Checklist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'IEEE 29148 PRD Checklist'!$A$1:$E$21</definedName>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="77">
   <si>
     <t>Category</t>
   </si>
@@ -79,9 +80,6 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Operating environment is only partly defined: owner's environment, browser access, local model (DC-01, DC-03, IF-02). No hardware specification or operating system. Action: define host hardware, OS and browser support.</t>
-  </si>
-  <si>
     <t>3. Functional Requirements</t>
   </si>
   <si>
@@ -100,9 +98,6 @@
     <t>Do the requirements state 'what' the system must do rather than 'how' it should be coded or architected?</t>
   </si>
   <si>
-    <t>Functional requirements state capabilities; technology appears only in Section 8 Design Constraints and DC-01. REQ-014 mentions the language model location, which comes from CON-001.</t>
-  </si>
-  <si>
     <t>Verifiable</t>
   </si>
   <si>
@@ -121,9 +116,6 @@
     <t>Are quantifiable metrics provided for speed, throughput, and capacity (e.g., 'Model inference latency &lt; 200ms')?</t>
   </si>
   <si>
-    <t>NFR-01 to NFR-04 give times and capacity (60 s, 30 s, 3 s, 1,200 devices, 50 alerts/min). Values are [Assumed]; confirm under OQ-P02.</t>
-  </si>
-  <si>
     <t>Security &amp; Privacy</t>
   </si>
   <si>
@@ -139,9 +131,6 @@
     <t>Are uptime SLAs, fault tolerance mechanisms, and recovery time objectives (RTO) explicitly stated?</t>
   </si>
   <si>
-    <t>NFR-05 (95 % availability), NFR-06 (4-hour recovery), NFR-07 (fallback to existing monitoring system). Values are [Assumed].</t>
-  </si>
-  <si>
     <t>Scalability</t>
   </si>
   <si>
@@ -160,9 +149,6 @@
     <t>Are the logical characteristics of the UI defined without dictating the exact visual design or layout?</t>
   </si>
   <si>
-    <t>Section 6.2 describes dashboard, incident detail, report and results views, and 8 error states, without fixing visual design.</t>
-  </si>
-  <si>
     <t>Hardware Interfaces</t>
   </si>
   <si>
@@ -181,9 +167,6 @@
     <t>Are integrations with external APIs, operating systems, databases, or legacy systems fully documented?</t>
   </si>
   <si>
-    <t>IF-01 to IF-04 list the monitoring system, browser, local model and report export. Data formats and access method for the monitoring system are unknown (ASM-002, OQ-P03). Action: close OQ-P03 and specify the interface.</t>
-  </si>
-  <si>
     <t>Communication Interfaces</t>
   </si>
   <si>
@@ -205,9 +188,6 @@
     <t>Are technology mandates, regulatory compliance (e.g., GDPR), and physical restrictions documented?</t>
   </si>
   <si>
-    <t>DC-01 to DC-05 cover local model, simulated data, hardware, time, budget and non-replacement of the monitoring system. Regulatory constraints: none identified (Section 3.4).</t>
-  </si>
-  <si>
     <t>Dependencies</t>
   </si>
   <si>
@@ -226,9 +206,6 @@
     <t>Is the language clear, avoiding subjective terms like 'fast', 'user-friendly', or 'robust'?</t>
   </si>
   <si>
-    <t>Numbers replace vague words in most requirements. Terms such as "plain language", "low confidence" and "probable" are not defined. NFR-11 uses "should" for accessibility. Action: define these terms in Section 1.5.</t>
-  </si>
-  <si>
     <t>Traceable &amp; Numbered</t>
   </si>
   <si>
@@ -244,34 +221,61 @@
     <t>Are there any conflicting requirements (e.g., one requiring maximum security and another requiring anonymous access)?</t>
   </si>
   <si>
-    <t>Reviewed for conflicts; none found. REQ-014 (local only) is consistent with IF-04 (local export) and DC-01.</t>
+    <t>Section 2.1 specifies: 16GB RAM, 100GB storage, Linux/Windows, Chrome/Firefox/Edge, local network isolation.</t>
+  </si>
+  <si>
+    <t>REQ-014 split into REQ-014 (local data processing) and REQ-14b (local model). Each has one obligation.</t>
+  </si>
+  <si>
+    <t>REQ-008 and REQ-010 now have measurable criteria: US-05 and US-09 with Given-When-Then; plain language verified by NOC reviewer rating.</t>
+  </si>
+  <si>
+    <t>REQ-015 with role permission matrix (Engineer/Team Lead/Admin). NFR-08, NFR-09 specify security. Encryption rule DC-06 added.</t>
+  </si>
+  <si>
+    <t>NFR-04 set at 1,200 devices, 50 alerts/min. NFR-14 added: stretch to 2,000 devices, 100 alerts/min. OQ-P07 tracks decision.</t>
+  </si>
+  <si>
+    <t>IF-01 to IF-05 specify protocols (HTTPS/TLS 1.2+, REST, JSON, gRPC) and data formats. OQ-P03 tracks monitoring system method.</t>
+  </si>
+  <si>
+    <t>Section 6.1 specifies: HTTPS/TLS 1.2+ (browser-Assistant), local HTTP/gRPC (internal), no external calls.</t>
+  </si>
+  <si>
+    <t>Section 8.1 added: DEP-01 (dataset), DEP-02 (model), DEP-03 (monitoring system), DEP-04 (institutional support).</t>
+  </si>
+  <si>
+    <t>Terms defined in Section 7 (NFR definitions) and Section 12.1 (plain language, evidence, probable cause, low confidence, incident, escalation, audit log).</t>
+  </si>
+  <si>
+    <t>Section 6.1 note: no direct hardware interface. System reaches devices only via monitoring system (IF-01).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color theme="1"/>
-      <family val="2"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
       <charset val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-      <name val="Cambria"/>
     </font>
   </fonts>
   <fills count="5">
@@ -327,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -347,6 +351,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,7 +369,18 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FF27AE60"/>
+          <bgColor rgb="FF95A5A6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE74C3C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -381,18 +402,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE74C3C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF95A5A6"/>
+          <bgColor rgb="FF27AE60"/>
         </patternFill>
       </fill>
     </dxf>
@@ -410,7 +420,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -452,12 +462,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -486,7 +496,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -507,7 +517,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -558,7 +568,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -576,28 +586,31 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.6796875"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" style="1" customWidth="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
     <col min="3" max="3" width="65" style="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
     <col min="5" max="5" width="35" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.68" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -614,8 +627,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -631,8 +644,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+    <row r="3" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
       <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
@@ -646,8 +659,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -663,8 +676,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
+    <row r="5" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
@@ -672,296 +685,301 @@
         <v>18</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="8" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+      <c r="B12" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="13" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="5" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="15" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="5" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="D18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="19" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="D19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="3" t="s">
+    </row>
+    <row r="21" spans="1:5" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+      <c r="B21" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="19" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" ht="28.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="5" t="s">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E21"/>
+  <autoFilter ref="A1:E21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="7">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A19:A21"/>
   </mergeCells>
   <conditionalFormatting sqref="D2:D21">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"Pending"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="D10:D21">
-      <formula1>"Pending,In Progress,Done,N/A"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D21">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D21" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Pending,In Progress,Done,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>